--- a/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026 BLACK BEAR EITHER SEX STATEWIDE ANY LEGAL WEAPON.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026 BLACK BEAR EITHER SEX STATEWIDE ANY LEGAL WEAPON.xlsx
@@ -611,7 +611,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Black Bear statewide permit: Any open season on any open bear unit during the 2026 season.</t>
+          <t>Includes all limited-entry season hunt dates. Any open season on any open bear unit during the 2026 season. See 2026 Black Bear Guidebook for season dates and take methods.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
